--- a/stories/arbres/ATOM-TMP.JOU.001-05.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le jour, Hector joue avec papa. Le soleil brille. Il fait chaud près de la fenêtre. Papa dit : le jour, c'est le soleil. Le soir arrive. Le ciel devient bleu foncé. Hector voit la lune. Il voit les étoiles. Papa dit : la nuit, c'est la lune. Hector met son pyjama. Le pyjama est doux. Papa dit : la nuit, on fait dodo. Hector se couche. Il ferme les yeux. Dodo la nuit.</t>
+          <t>Le jour, Hector joue avec papa. Le soleil brille. Il fait chaud près de la fenêtre. Le jour, c'est le soleil. Le soir arrive. Le ciel devient bleu foncé. Hector voit la lune. Il voit les étoiles. La nuit, c'est la lune. Hector met son pyjama. Le pyjama est doux. La nuit, on fait dodo. Hector se couche. Il ferme les yeux. Dodo la nuit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le jour, Hector joue avec papa. Le soleil brille. Il fait chaud près de la fenêtre.
+papa|Le jour, c'est le soleil.
+narrateur|Le soir arrive. Le ciel devient bleu foncé. Hector voit la lune. Il voit les étoiles.
+papa|La nuit, c'est la lune.
+narrateur|Hector met son pyjama. Le pyjama est doux.
+papa|La nuit, on fait dodo.
+narrateur|Hector se couche. Il ferme les yeux. Dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La lune est là. Quel moment est-ce ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hector a vu le soleil le jour. Il a vu la lune la nuit. Il fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1836,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa baisse la lumière. Hector respire.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2003,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-05.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Hector se couche. Il ferme les yeux. Dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|La lune est là. Quel moment est-ce ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Hector a vu le soleil le jour. Il a vu la lune la nuit. Il fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1849,7 @@
           <t>narrateur|Papa baisse la lumière. Hector respire.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.JOU.001-05.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hector voit le soleil et la lune</t>
+          <t>Le chat du mur de Chouchou</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou veut le chat du mur. Le soleil cligne sur les toits. Un pigeon fait fuir le chat. Le soir, la lune est sur le zinc, le chat revient.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le jour, Hector joue avec papa. Le soleil brille. Il fait chaud près de la fenêtre. Le jour, c'est le soleil. Le soir arrive. Le ciel devient bleu foncé. Hector voit la lune. Il voit les étoiles. La nuit, c'est la lune. Hector met son pyjama. Le pyjama est doux. La nuit, on fait dodo. Hector se couche. Il ferme les yeux. Dodo la nuit.</t>
+          <t>Les toits de zinc clignent sous le soleil. Le balcon sent le linge chaud. Une gouttière tient une feuille sèche. Le mur d'en face est déjà brûlant. Tu as vu le zinc, Chouchou ? Il brille. Oui. Les toits sont chauds. Je veux le chat. Il vient sur le mur. En ce moment, Chouchou s'accoude. Le fer du balcon est chaud. Le soleil tape les toits, fort. Le jour est clair. Le soleil est sur les toits. Un chat gris arrive sur le mur. Il se frotte, lent. Il est là. Tout doux. Un pigeon se pose, brusque. Le chat saute, disparu. Oh. Il est parti. Il reviendra. On attend ? Oui. Chouchou reste accoudée. Une lessive claque, à côté. Une radio chante, loin. Un camion passe en bas, sourd. Il tarde. Le jour est encore long. Une goutte tombe de la gouttière. Elle sèche sur le zinc, vite. L'ombre du mur s'allonge. Le zinc perd son clignement. Le ciel devient bleu foncé. Une lune ronde s'assoit sur un toit. Elle est sur le zinc. La nuit est là. La lune est sur les toits. Le chat revient, plus silencieux. Le voilà. Merci d'avoir attendu. Tu as été patiente.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le jour, Hector joue avec papa. Le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; brille. Il fait chaud près de la fenêtre. Papa dit : le jour, c'est le soleil. Le soir arrive. Le ciel devient bleu foncé. Hector voit la lune. Il voit les étoiles. Papa dit : la nuit, c'est la lune. Hector met son pyjama. Le pyjama est doux. Papa dit : la nuit, on fait dodo. Hector se couche. Il ferme les yeux. Dodo la nuit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les toits de zinc clignent sous le soleil. Le balcon sent le linge chaud. Une gouttière tient une feuille sèche. Le mur d'en face est déjà brûlant. Tu as vu le zinc, Chouchou ? Il brille. Oui. Les toits sont chauds. Je veux le chat. Il vient sur le mur. En ce moment, Chouchou s'accoude. Le fer du balcon est chaud. Le soleil tape les toits, fort. Le jour est clair. Le soleil est sur les toits. Un chat gris arrive sur le mur. Il se frotte, lent. Il est là. Tout doux. Un pigeon se pose, brusque. Le chat saute, disparu. Oh. Il est parti. Il reviendra. On attend ? Oui. Chouchou reste accoudée. Une lessive claque, à côté. Une radio chante, loin. Un camion passe en bas, sourd. Il tarde. Le jour est encore long. Une goutte tombe de la gouttière. Elle sèche sur le zinc, vite. L'ombre du mur s'allonge. Le zinc perd son clignement. Le ciel devient bleu foncé. Une lune ronde s'assoit sur un toit. Elle est sur le zinc. La nuit est là. La lune est sur les toits. Le chat revient, plus silencieux. Le voilà. Merci d'avoir attendu. Tu as été patiente.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,16 +1324,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le jour, Hector joue avec papa. Le soleil brille. Il fait chaud près de la fenêtre.
-papa|Le jour, c'est le soleil.
-narrateur|Le soir arrive. Le ciel devient bleu foncé. Hector voit la lune. Il voit les étoiles.
-papa|La nuit, c'est la lune.
-narrateur|Hector met son pyjama. Le pyjama est doux.
-papa|La nuit, on fait dodo.
-narrateur|Hector se couche. Il ferme les yeux. Dodo la nuit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les toits de zinc clignent sous le soleil.
+narrateur|Le balcon sent le linge chaud.
+narrateur|Une gouttière tient une feuille sèche.
+narrateur|Le mur d'en face est déjà brûlant.
+papa|Tu as vu le zinc, Chouchou ?
+enfant-f|Il brille.
+papa|Oui.
+papa|Les toits sont chauds.
+enfant-f|Je veux le chat.
+papa|Il vient sur le mur.
+narrateur|En ce moment, Chouchou s'accoude.
+narrateur|Le fer du balcon est chaud.
+narrateur|Le soleil tape les toits, fort.
+papa|Le jour est clair.
+papa|Le soleil est sur les toits.
+narrateur|Un chat gris arrive sur le mur.
+narrateur|Il se frotte, lent.
+enfant-f|Il est là.
+papa|Tout doux.
+narrateur|Un pigeon se pose, brusque.
+narrateur|Le chat saute, disparu.
+enfant-f|Oh.
+enfant-f|Il est parti.
+papa|Il reviendra.
+papa|On attend ?
+enfant-f|Oui.
+narrateur|Chouchou reste accoudée.
+narrateur|Une lessive claque, à côté.
+narrateur|Une radio chante, loin.
+narrateur|Un camion passe en bas, sourd.
+enfant-f|Il tarde.
+papa|Le jour est encore long.
+narrateur|Une goutte tombe de la gouttière.
+narrateur|Elle sèche sur le zinc, vite.
+narrateur|L'ombre du mur s'allonge.
+narrateur|Le zinc perd son clignement.
+narrateur|Le ciel devient bleu foncé.
+narrateur|Une lune ronde s'assoit sur un toit.
+enfant-f|Elle est sur le zinc.
+papa|La nuit est là.
+papa|La lune est sur les toits.
+narrateur|Le chat revient, plus silencieux.
+enfant-f|Le voilà.
+papa|Merci d'avoir attendu.
+papa|Tu as été patiente.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>ville</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,12 +1400,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La lune est là. Quel moment est-ce ?</t>
+          <t>La lune est sur le toit. Quel moment est-ce ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;lune&lt;/emphasis&gt; est là. Quel moment est-ce ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La lune est sur le toit. Quel moment est-ce ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1366,7 +1420,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>nuit | la nuit | lune | le soir</t>
+          <t>nuit | la nuit | le soir | dodo | c'est la nuit</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1381,7 +1435,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>La lune vient la nuit. Quel moment ?</t>
+          <t>La lune est sur le toit. C'est le jour, ou la nuit ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1430,7 +1484,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1560,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La lune est là. Quel moment est-ce ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La lune est sur le toit.
+narrateur|Quel moment est-ce ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,12 +1588,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hector a vu le soleil le jour. Il a vu la lune la nuit. Il fait dodo la nuit.</t>
+          <t>Chouchou a vu le zinc tout brillant. Maintenant la lune est sur le même toit. Le jour, c'était le soleil. La nuit, c'est la lune. Le chat est revenu. Oui. On rentre se coucher ? Encore le chat. Le chat se lèche une patte. La gouttière tient encore sa feuille. Tu lui dis au revoir ? À demain. Le linge ne claque plus. L'air du balcon est plus frais.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hector a vu le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; le jour. Il a vu la lune la nuit. Il fait dodo la nuit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a vu le zinc tout brillant. Maintenant la lune est sur le même toit. Le jour, c'était le soleil. La nuit, c'est la lune. Le chat est revenu. Oui. On rentre se coucher ? Encore le chat. Le chat se lèche une patte. La gouttière tient encore sa feuille. Tu lui dis au revoir ? À demain. Le linge ne claque plus. L'air du balcon est plus frais.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1595,14 +1649,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1678,10 +1732,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hector a vu le soleil le jour. Il a vu la lune la nuit. Il fait dodo la nuit.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Chouchou a vu le zinc tout brillant.
+narrateur|Maintenant la lune est sur le même toit.
+papa|Le jour, c'était le soleil.
+papa|La nuit, c'est la lune.
+enfant-f|Le chat est revenu.
+papa|Oui.
+papa|On rentre se coucher ?
+enfant-f|Encore le chat.
+narrateur|Le chat se lèche une patte.
+narrateur|La gouttière tient encore sa feuille.
+papa|Tu lui dis au revoir ?
+enfant-f|À demain.
+narrateur|Le linge ne claque plus.
+narrateur|L'air du balcon est plus frais.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,12 +1772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa baisse la lumière. Hector respire.</t>
+          <t>Chouchou quitte le fer du balcon. Le fer est plus froid, maintenant. Le pyjama, maintenant. Le pyjama sent le linge du balcon. La lune est encore là ? À la fenêtre. Chouchou monte sur le lit. Le zinc est gris, dehors. La lune tient encore un coin de toit. La nuit, on fait dodo. Tu fermes les yeux ? Presque. Papa baisse la lumière. Chouchou respire le linge chaud.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa bais&lt;emphasis level="moderate"&gt;se&lt;/emphasis&gt; la lumière. Hector respire.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou quitte le fer du balcon. Le fer est plus froid, maintenant. Le pyjama, maintenant. Le pyjama sent le linge du balcon. La lune est encore là ? À la fenêtre. Chouchou monte sur le lit. Le zinc est gris, dehors. La lune tient encore un coin de toit. La nuit, on fait dodo. Tu fermes les yeux ? Presque. Papa baisse la lumière. Chouchou respire le linge chaud.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1767,14 +1833,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1846,10 +1912,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa baisse la lumière. Hector respire.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Chouchou quitte le fer du balcon.
+narrateur|Le fer est plus froid, maintenant.
+papa|Le pyjama, maintenant.
+narrateur|Le pyjama sent le linge du balcon.
+enfant-f|La lune est encore là ?
+papa|À la fenêtre.
+narrateur|Chouchou monte sur le lit.
+narrateur|Le zinc est gris, dehors.
+narrateur|La lune tient encore un coin de toit.
+papa|La nuit, on fait dodo.
+papa|Tu fermes les yeux ?
+enfant-f|Presque.
+narrateur|Papa baisse la lumière.
+narrateur|Chouchou respire le linge chaud.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1874,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le chat reste une tache sur le mur. La lune reste une tache sur le zinc. Il est revenu. Oui. Toi aussi, tu as attendu. Chouchou ferme les yeux. La gouttière ne bouge plus.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chat reste une tache sur le mur. La lune reste une tache sur le zinc. Il est revenu. Oui. Toi aussi, tu as attendu. Chouchou ferme les yeux. La gouttière ne bouge plus.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1935,14 +2013,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2014,10 +2092,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le chat reste une tache sur le mur.
+narrateur|La lune reste une tache sur le zinc.
+enfant-f|Il est revenu.
+papa|Oui.
+papa|Toi aussi, tu as attendu.
+narrateur|Chouchou ferme les yeux.
+narrateur|La gouttière ne bouge plus.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2036,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2157,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-05.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fenêtre puis chambre</t>
+          <t>balcon en ville</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hector, papa</t>
+          <t>Chouchou, papa</t>
         </is>
       </c>
     </row>
